--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="73">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t xml:space="preserve">Промпты для ИИ-агентов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Наполнен (Release 1.1): 13 промптов по 6 агентам, сгруппированы по типу документа</t>
   </si>
   <si>
     <t xml:space="preserve">08_Карточки_оборудования</t>
@@ -349,8 +352,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -646,429 +653,429 @@
   <dimension ref="A1:D30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="42"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+    <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+      <c r="D4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="D5" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+      <c r="D6" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="D7" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+      <c r="D8" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+      <c r="D9" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="B24" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="B25" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="B26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="B27" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="n">
         <v>27</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="B28" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="B29" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="C30" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>12</v>
       </c>
     </row>

--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Стандарты диагностики</t>
   </si>
   <si>
-    <t xml:space="preserve">СТД-001 утверждён; СТД-002, СТД-003 в черновике</t>
+    <t xml:space="preserve">Наполнен: СТД-001, СТД-002, СТД-003 утверждены (v1.0). СТД-002/003 — по открытым данным, требуют привязки к объекту</t>
   </si>
   <si>
     <t xml:space="preserve">02_Регламенты_РГЛ</t>

--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="75">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -61,19 +61,25 @@
     <t xml:space="preserve">Регламенты обслуживания</t>
   </si>
   <si>
+    <t xml:space="preserve">Наполнен: РГЛ-001 утверждён (v1.0), по открытым данным, требует привязки к объекту</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03_Инструкции_ИНС</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Инструкции для персонала</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В работе: ИНС-001 v0.9 на редакции (в 20_На_редакции), ожидает закрытия раздела «Типичные ошибки»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04_Энциклопедия</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Теоретические материалы (ЭНЦ)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Структура создана, ожидает наполнения</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03_Инструкции_ИНС</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Инструкции для персонала</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04_Энциклопедия</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Теоретические материалы (ЭНЦ)</t>
   </si>
   <si>
     <t xml:space="preserve">05_FAQ</t>
@@ -726,7 +732,7 @@
         <v>14</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -734,13 +740,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -748,13 +754,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -762,13 +768,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -776,13 +782,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -790,13 +796,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -804,13 +810,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -818,13 +824,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -832,13 +838,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -846,13 +852,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -860,13 +866,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -874,13 +880,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -888,13 +894,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -902,13 +908,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -916,13 +922,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -930,13 +936,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -944,13 +950,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -958,13 +964,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -972,13 +978,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -986,13 +992,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1000,13 +1006,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1014,13 +1020,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1028,13 +1034,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1042,13 +1048,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1056,13 +1062,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1070,13 +1076,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="76">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -79,13 +79,16 @@
     <t xml:space="preserve">Теоретические материалы (ЭНЦ)</t>
   </si>
   <si>
+    <t xml:space="preserve">Наполнен: ЭНЦ-001, ЭНЦ-002, ЭНЦ-003 утверждены (v1.0), связаны с СТД-001/002/003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Часто задаваемые вопросы</t>
+  </si>
+  <si>
     <t xml:space="preserve">Структура создана, ожидает наполнения</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05_FAQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Часто задаваемые вопросы</t>
   </si>
   <si>
     <t xml:space="preserve">06_RAG</t>
@@ -760,7 +763,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -768,13 +771,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -782,13 +785,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -796,13 +799,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -810,13 +813,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -824,13 +827,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -838,13 +841,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -852,13 +855,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -866,13 +869,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -880,13 +883,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -894,13 +897,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -908,13 +911,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -922,13 +925,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -936,13 +939,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -950,13 +953,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -964,13 +967,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -978,13 +981,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -992,13 +995,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1006,13 +1009,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1020,13 +1023,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1034,13 +1037,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1048,13 +1051,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1062,13 +1065,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1076,13 +1079,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="77">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -88,13 +88,16 @@
     <t xml:space="preserve">Часто задаваемые вопросы</t>
   </si>
   <si>
+    <t xml:space="preserve">Наполнен: 6 FAQ утверждены (v1.0), сформированы на основе СТД-001/002/003, РГЛ-001, ИНС-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_RAG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-карточки</t>
+  </si>
+  <si>
     <t xml:space="preserve">Структура создана, ожидает наполнения</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06_RAG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAG-карточки</t>
   </si>
   <si>
     <t xml:space="preserve">07_Промпты</t>
@@ -777,7 +780,7 @@
         <v>23</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -785,13 +788,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -799,13 +802,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -813,13 +816,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -827,13 +830,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -841,13 +844,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -855,13 +858,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -869,13 +872,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -883,13 +886,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -897,13 +900,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -911,13 +914,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -925,13 +928,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -939,13 +942,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -953,13 +956,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -967,13 +970,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -981,13 +984,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -995,13 +998,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1009,13 +1012,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1023,13 +1026,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1037,13 +1040,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1051,13 +1054,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1065,13 +1068,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1079,13 +1082,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="78">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -97,22 +97,25 @@
     <t xml:space="preserve">RAG-карточки</t>
   </si>
   <si>
+    <t xml:space="preserve">Наполнен: 10 RAG-карточек утверждены (v1.0), нарезаны из СТД-001/002/003, РГЛ-001, ЭНЦ-001, ИНС-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07_Промпты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Промпты для ИИ-агентов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Наполнен (Release 1.1): 13 промптов по 6 агентам, сгруппированы по типу документа</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08_Карточки_оборудования</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Карточки оборудования</t>
+  </si>
+  <si>
     <t xml:space="preserve">Структура создана, ожидает наполнения</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07_Промпты</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Промпты для ИИ-агентов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Наполнен (Release 1.1): 13 промптов по 6 агентам, сгруппированы по типу документа</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08_Карточки_оборудования</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Карточки оборудования</t>
   </si>
   <si>
     <t xml:space="preserve">09_Технический_словарь</t>
@@ -808,7 +811,7 @@
         <v>29</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -816,13 +819,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -830,13 +833,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -844,13 +847,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -858,13 +861,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -872,13 +875,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -886,13 +889,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -900,13 +903,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -914,13 +917,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -928,13 +931,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -942,13 +945,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -956,13 +959,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -970,13 +973,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -984,13 +987,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -998,13 +1001,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1012,13 +1015,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1026,13 +1029,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1040,13 +1043,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1054,13 +1057,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1068,13 +1071,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1082,13 +1085,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="79">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -131,6 +131,9 @@
   </si>
   <si>
     <t xml:space="preserve">Классификатор неисправностей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Наполнен: 7 неисправностей (v1.0), закрывают ссылки из СТД/ЭНЦ/RAG. Колонка «Типовое решение» ждёт наполнения 12_Типовые_решения</t>
   </si>
   <si>
     <t xml:space="preserve">11_Физика_процессов</t>
@@ -839,7 +842,7 @@
         <v>35</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -847,10 +850,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>30</v>
@@ -861,10 +864,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>30</v>
@@ -875,10 +878,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>30</v>
@@ -889,10 +892,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>30</v>
@@ -903,10 +906,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>30</v>
@@ -917,10 +920,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>30</v>
@@ -931,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -945,13 +948,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -959,13 +962,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -973,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -987,13 +990,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1001,13 +1004,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1015,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1029,13 +1032,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1043,13 +1046,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1057,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1071,10 +1074,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>30</v>
@@ -1085,10 +1088,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>30</v>

--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="80">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -133,7 +133,7 @@
     <t xml:space="preserve">Классификатор неисправностей</t>
   </si>
   <si>
-    <t xml:space="preserve">Наполнен: 7 неисправностей (v1.0), закрывают ссылки из СТД/ЭНЦ/RAG. Колонка «Типовое решение» ждёт наполнения 12_Типовые_решения</t>
+    <t xml:space="preserve">Наполнен: 7 неисправностей (v1.1), колонка «Типовое решение» теперь ссылается на конкретные РЕШ-00X</t>
   </si>
   <si>
     <t xml:space="preserve">11_Физика_процессов</t>
@@ -146,6 +146,9 @@
   </si>
   <si>
     <t xml:space="preserve">Типовые решения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Наполнен: 7 решений (v1.0), 1:1 с 10_Каталог_неисправностей</t>
   </si>
   <si>
     <t xml:space="preserve">13_Кейсы_объектов</t>
@@ -870,7 +873,7 @@
         <v>40</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -878,10 +881,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>30</v>
@@ -892,10 +895,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>30</v>
@@ -906,10 +909,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>30</v>
@@ -920,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>30</v>
@@ -934,13 +937,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -948,13 +951,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -962,13 +965,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -976,13 +979,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -990,13 +993,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1004,13 +1007,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1018,13 +1021,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1032,13 +1035,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1046,13 +1049,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1060,13 +1063,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1074,10 +1077,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>30</v>
@@ -1088,10 +1091,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>30</v>

--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="81">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -115,33 +115,36 @@
     <t xml:space="preserve">Карточки оборудования</t>
   </si>
   <si>
+    <t xml:space="preserve">Наполнен: шаблон ШБ-009 + 3 примера (КАР-001/002/003), требуют замены на реальные данные объекта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_Технический_словарь</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Единая терминология</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Начальный состав внесён в Реестр_терминов.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10_Каталог_неисправностей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Классификатор неисправностей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Наполнен: 7 неисправностей (v1.1), колонка «Типовое решение» теперь ссылается на конкретные РЕШ-00X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11_Физика_процессов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Физические принципы диагностики</t>
+  </si>
+  <si>
     <t xml:space="preserve">Структура создана, ожидает наполнения</t>
   </si>
   <si>
-    <t xml:space="preserve">09_Технический_словарь</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Единая терминология</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Начальный состав внесён в Реестр_терминов.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10_Каталог_неисправностей</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Классификатор неисправностей</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Наполнен: 7 неисправностей (v1.1), колонка «Типовое решение» теперь ссылается на конкретные РЕШ-00X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11_Физика_процессов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Физические принципы диагностики</t>
-  </si>
-  <si>
     <t xml:space="preserve">12_Типовые_решения</t>
   </si>
   <si>
@@ -181,7 +184,7 @@
     <t xml:space="preserve">Шаблоны документов</t>
   </si>
   <si>
-    <t xml:space="preserve">Наполнен (Foundation): ШБ-001…ШБ-008</t>
+    <t xml:space="preserve">Наполнен (Foundation): ШБ-001…ШБ-009</t>
   </si>
   <si>
     <t xml:space="preserve">18_ИИ_Агенты</t>
@@ -859,7 +862,7 @@
         <v>38</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -867,13 +870,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -881,13 +884,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -895,13 +898,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -909,13 +912,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -923,13 +926,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -937,13 +940,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -951,13 +954,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -965,13 +968,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -979,13 +982,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -993,13 +996,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1007,13 +1010,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1021,13 +1024,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1035,13 +1038,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1049,13 +1052,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1063,13 +1066,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1077,13 +1080,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1091,13 +1094,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="82">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -158,6 +158,9 @@
   </si>
   <si>
     <t xml:space="preserve">Кейсы объектов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Наполнен: 2 иллюстративных примера (КЕЙС-001/002), демонстрируют полный цикл диагностика→неисправность→решение</t>
   </si>
   <si>
     <t xml:space="preserve">14_Фотоархив</t>
@@ -890,7 +893,7 @@
         <v>44</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -898,10 +901,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>39</v>
@@ -912,10 +915,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>39</v>
@@ -926,10 +929,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>39</v>
@@ -940,13 +943,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -954,13 +957,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -968,13 +971,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -982,13 +985,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -996,13 +999,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1010,13 +1013,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1024,13 +1027,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1038,13 +1041,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1052,13 +1055,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1066,13 +1069,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1080,10 +1083,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>39</v>
@@ -1094,10 +1097,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>39</v>

--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="83">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -142,31 +142,34 @@
     <t xml:space="preserve">Физические принципы диагностики</t>
   </si>
   <si>
+    <t xml:space="preserve">Зарезервирован: содержание консолидировано в 04_Энциклопедия (см. README раздела 11 — явная переадресация)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12_Типовые_решения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Типовые решения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Наполнен: 7 решений (v1.0), 1:1 с 10_Каталог_неисправностей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13_Кейсы_объектов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кейсы объектов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Наполнен: 2 иллюстративных примера (КЕЙС-001/002), демонстрируют полный цикл диагностика→неисправность→решение</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14_Фотоархив</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фотоматериалы</t>
+  </si>
+  <si>
     <t xml:space="preserve">Структура создана, ожидает наполнения</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12_Типовые_решения</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Типовые решения</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Наполнен: 7 решений (v1.0), 1:1 с 10_Каталог_неисправностей</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13_Кейсы_объектов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кейсы объектов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Наполнен: 2 иллюстративных примера (КЕЙС-001/002), демонстрируют полный цикл диагностика→неисправность→решение</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14_Фотоархив</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Фотоматериалы</t>
   </si>
   <si>
     <t xml:space="preserve">15_Видеоархив</t>
@@ -907,7 +910,7 @@
         <v>47</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -915,13 +918,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -929,13 +932,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -943,13 +946,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -957,13 +960,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -971,13 +974,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -985,13 +988,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -999,13 +1002,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1013,13 +1016,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1027,13 +1030,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1041,13 +1044,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1055,13 +1058,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1069,13 +1072,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1083,13 +1086,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1097,13 +1100,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="84">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -97,7 +97,7 @@
     <t xml:space="preserve">RAG-карточки</t>
   </si>
   <si>
-    <t xml:space="preserve">Наполнен: 10 RAG-карточек утверждены (v1.0), нарезаны из СТД-001/002/003, РГЛ-001, ЭНЦ-001, ИНС-001</t>
+    <t xml:space="preserve">Наполнен: 10 RAG-карточек (v1.0, RAG-0007..0010 не затронуты правкой; v1.1 — RAG-0001..0006 после исправления битой ссылки на источник)</t>
   </si>
   <si>
     <t xml:space="preserve">07_Промпты</t>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t xml:space="preserve">Аналитика по базе знаний</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Наполнен: АУДИТ-001 — первый формальный сквозной аудит проекта (v1.0)</t>
   </si>
   <si>
     <t xml:space="preserve">28_Лаборатория</t>
@@ -1092,7 +1095,7 @@
         <v>80</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1100,10 +1103,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>48</v>

--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="85">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -124,7 +124,7 @@
     <t xml:space="preserve">Единая терминология</t>
   </si>
   <si>
-    <t xml:space="preserve">Начальный состав внесён в Реестр_терминов.xlsx</t>
+    <t xml:space="preserve">Наполнен: Технический_словарь.docx (v1.1, 29 терминов) — включая термины из ФЗ №190/ГОСТ 22270/СП 124.13330</t>
   </si>
   <si>
     <t xml:space="preserve">10_Каталог_неисправностей</t>
@@ -182,6 +182,9 @@
   </si>
   <si>
     <t xml:space="preserve">Внешние нормативные документы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Наполнен: НД-001 — индекс 3 внешних нормативных документов (v1.0)</t>
   </si>
   <si>
     <t xml:space="preserve">17_Шаблоны</t>
@@ -941,7 +944,7 @@
         <v>52</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -949,13 +952,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -963,13 +966,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -977,13 +980,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -991,13 +994,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1005,13 +1008,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1019,13 +1022,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1033,13 +1036,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1047,13 +1050,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1061,13 +1064,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1075,13 +1078,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1089,13 +1092,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1103,10 +1106,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>48</v>

--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -70,7 +70,7 @@
     <t xml:space="preserve">Инструкции для персонала</t>
   </si>
   <si>
-    <t xml:space="preserve">В работе: ИНС-001 v0.9 на редакции (в 20_На_редакции), ожидает закрытия раздела «Типичные ошибки»</t>
+    <t xml:space="preserve">Наполнен: ИНС-001 утверждён (v1.0) — Типичные ошибки на основе 6 реальных задокументированных отраслевых случаев</t>
   </si>
   <si>
     <t xml:space="preserve">04_Энциклопедия</t>

--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -253,7 +253,7 @@
     <t xml:space="preserve">Архив устаревших версий</t>
   </si>
   <si>
-    <t xml:space="preserve">Пуст на момент Release 1.0</t>
+    <t xml:space="preserve">Наполнен: 9 архивных версий восстановлены из git (v1.0 журнала); процесс архивирования восстановлен согласно КП-005</t>
   </si>
   <si>
     <t xml:space="preserve">26_Релизы</t>

--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -262,7 +262,7 @@
     <t xml:space="preserve">Релизы базы знаний</t>
   </si>
   <si>
-    <t xml:space="preserve">Release_1.0_FOUNDATION опубликован</t>
+    <t xml:space="preserve">Наполнен: Release_1.0_FOUNDATION опубликован; Release_1.1 формально утверждён (v1.1) — консолидирует все изменения, добавлены замороженные снимки реестров</t>
   </si>
   <si>
     <t xml:space="preserve">27_Аналитика</t>

--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Регламенты обслуживания</t>
   </si>
   <si>
-    <t xml:space="preserve">Наполнен: РГЛ-001 утверждён (v1.0), по открытым данным, требует привязки к объекту</t>
+    <t xml:space="preserve">Наполнен: РГЛ-001/002/003 утверждены — теперь по регламенту на каждый тип оборудования (теплообменник/котёл/насос)</t>
   </si>
   <si>
     <t xml:space="preserve">03_Инструкции_ИНС</t>
@@ -253,7 +253,7 @@
     <t xml:space="preserve">Архив устаревших версий</t>
   </si>
   <si>
-    <t xml:space="preserve">Наполнен: 9 архивных версий восстановлены из git (v1.0 журнала); процесс архивирования восстановлен согласно КП-005</t>
+    <t xml:space="preserve">Наполнен: 11 архивных версий (журнал v1.1); процесс архивирования соблюдается на практике с 11.07.2026</t>
   </si>
   <si>
     <t xml:space="preserve">26_Релизы</t>

--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -271,7 +271,7 @@
     <t xml:space="preserve">Аналитика по базе знаний</t>
   </si>
   <si>
-    <t xml:space="preserve">Наполнен: АУДИТ-001 — первый формальный сквозной аудит проекта (v1.0)</t>
+    <t xml:space="preserve">Наполнен: АУДИТ-001, АУДИТ-002 — регулярные сквозные аудиты проекта, оба с найденными и устранёнными замечаниями</t>
   </si>
   <si>
     <t xml:space="preserve">28_Лаборатория</t>

--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -97,7 +97,7 @@
     <t xml:space="preserve">RAG-карточки</t>
   </si>
   <si>
-    <t xml:space="preserve">Наполнен: 10 RAG-карточек (v1.0, RAG-0007..0010 не затронуты правкой; v1.1 — RAG-0001..0006 после исправления битой ссылки на источник)</t>
+    <t xml:space="preserve">Наполнен: 14 RAG-карточек утверждены — из СТД-001/002/003, РГЛ-001/002/003, ЭНЦ-001, ИНС-001</t>
   </si>
   <si>
     <t xml:space="preserve">07_Промпты</t>
@@ -160,7 +160,7 @@
     <t xml:space="preserve">Кейсы объектов</t>
   </si>
   <si>
-    <t xml:space="preserve">Наполнен: 2 иллюстративных примера (КЕЙС-001/002), демонстрируют полный цикл диагностика→неисправность→решение</t>
+    <t xml:space="preserve">Наполнен: 3 иллюстративных примера (КЕЙС-001/002/003) — по одному на каждый тип оборудования</t>
   </si>
   <si>
     <t xml:space="preserve">14_Фотоархив</t>

--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Стандарты диагностики</t>
   </si>
   <si>
-    <t xml:space="preserve">Наполнен: СТД-001, СТД-002, СТД-003 утверждены (v1.0). СТД-002/003 — по открытым данным, требуют привязки к объекту</t>
+    <t xml:space="preserve">Наполнен: СТД-001…005 утверждены — все распространённые виды котлов (газ/жидкое, электро, твердотопливные) + теплообменник + насос</t>
   </si>
   <si>
     <t xml:space="preserve">02_Регламенты_РГЛ</t>
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Регламенты обслуживания</t>
   </si>
   <si>
-    <t xml:space="preserve">Наполнен: РГЛ-001/002/003 утверждены — теперь по регламенту на каждый тип оборудования (теплообменник/котёл/насос)</t>
+    <t xml:space="preserve">Наполнен: РГЛ-001…005 утверждены — регламент на каждый тип оборудования из 01_Стандарты_СТД</t>
   </si>
   <si>
     <t xml:space="preserve">03_Инструкции_ИНС</t>
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Теоретические материалы (ЭНЦ)</t>
   </si>
   <si>
-    <t xml:space="preserve">Наполнен: ЭНЦ-001, ЭНЦ-002, ЭНЦ-003 утверждены (v1.0), связаны с СТД-001/002/003</t>
+    <t xml:space="preserve">Наполнен: ЭНЦ-001…005 утверждены, связаны с соответствующими СТД</t>
   </si>
   <si>
     <t xml:space="preserve">05_FAQ</t>
@@ -97,7 +97,7 @@
     <t xml:space="preserve">RAG-карточки</t>
   </si>
   <si>
-    <t xml:space="preserve">Наполнен: 14 RAG-карточек утверждены — из СТД-001/002/003, РГЛ-001/002/003, ЭНЦ-001, ИНС-001</t>
+    <t xml:space="preserve">Наполнен: 18 RAG-карточек утверждены — из всех СТД/РГЛ/ЭНЦ/ИНС</t>
   </si>
   <si>
     <t xml:space="preserve">07_Промпты</t>
@@ -124,7 +124,7 @@
     <t xml:space="preserve">Единая терминология</t>
   </si>
   <si>
-    <t xml:space="preserve">Наполнен: Технический_словарь.docx (v1.1, 29 терминов) — включая термины из ФЗ №190/ГОСТ 22270/СП 124.13330</t>
+    <t xml:space="preserve">Наполнен: Технический_словарь.docx (v1.2, 33 термина)</t>
   </si>
   <si>
     <t xml:space="preserve">10_Каталог_неисправностей</t>
@@ -133,7 +133,7 @@
     <t xml:space="preserve">Классификатор неисправностей</t>
   </si>
   <si>
-    <t xml:space="preserve">Наполнен: 7 неисправностей (v1.1), колонка «Типовое решение» теперь ссылается на конкретные РЕШ-00X</t>
+    <t xml:space="preserve">Наполнен: 11 неисправностей (v1.2), покрывают все 5 типов оборудования</t>
   </si>
   <si>
     <t xml:space="preserve">11_Физика_процессов</t>
@@ -151,7 +151,7 @@
     <t xml:space="preserve">Типовые решения</t>
   </si>
   <si>
-    <t xml:space="preserve">Наполнен: 7 решений (v1.0), 1:1 с 10_Каталог_неисправностей</t>
+    <t xml:space="preserve">Наполнен: 11 решений (v1.1), 1:1 с каталогом неисправностей</t>
   </si>
   <si>
     <t xml:space="preserve">13_Кейсы_объектов</t>
@@ -393,15 +393,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>

--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -115,7 +115,7 @@
     <t xml:space="preserve">Карточки оборудования</t>
   </si>
   <si>
-    <t xml:space="preserve">Наполнен: шаблон ШБ-009 + 3 примера (КАР-001/002/003), требуют замены на реальные данные объекта</t>
+    <t xml:space="preserve">Наполнен: шаблон ШБ-009 + 5 примеров (КАР-001…005), по одному на каждый тип оборудования</t>
   </si>
   <si>
     <t xml:space="preserve">09_Технический_словарь</t>
@@ -160,7 +160,7 @@
     <t xml:space="preserve">Кейсы объектов</t>
   </si>
   <si>
-    <t xml:space="preserve">Наполнен: 3 иллюстративных примера (КЕЙС-001/002/003) — по одному на каждый тип оборудования</t>
+    <t xml:space="preserve">Наполнен: 5 иллюстративных примеров (КЕЙС-001…005) — по одному на каждый тип оборудования</t>
   </si>
   <si>
     <t xml:space="preserve">14_Фотоархив</t>
@@ -393,15 +393,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>

--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -88,7 +88,7 @@
     <t xml:space="preserve">Часто задаваемые вопросы</t>
   </si>
   <si>
-    <t xml:space="preserve">Наполнен: 6 FAQ утверждены (v1.0), сформированы на основе СТД-001/002/003, РГЛ-001, ИНС-001</t>
+    <t xml:space="preserve">Наполнен: 6 FAQ для персонала (утверждено) + 10 FAQ для клиентов в подразделе Клиенты/ (на редакции, ждут проверки перед публикацией)</t>
   </si>
   <si>
     <t xml:space="preserve">06_RAG</t>

--- a/00_Проект/MANIFEST.xlsx
+++ b/00_Проект/MANIFEST.xlsx
@@ -88,7 +88,7 @@
     <t xml:space="preserve">Часто задаваемые вопросы</t>
   </si>
   <si>
-    <t xml:space="preserve">Наполнен: 6 FAQ для персонала (утверждено) + 10 FAQ для клиентов в подразделе Клиенты/ (на редакции, ждут проверки перед публикацией)</t>
+    <t xml:space="preserve">Наполнен: 6 FAQ для персонала (утверждено) + 38 клиентских FAQ в 5 сегментах (Жители_МКД, Частные_дома, УК_ЖКХ, Юрлица, Инфраструктура_ГВС) — все на редакции</t>
   </si>
   <si>
     <t xml:space="preserve">06_RAG</t>
